--- a/artfynd/A 31293-2026 artfynd.xlsx
+++ b/artfynd/A 31293-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY388"/>
+  <dimension ref="A1:AZ388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387349</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387350</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384604</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384545</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384549</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384562</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384564</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387338</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387339</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387340</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384539</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1860,6 +1920,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610267</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611787</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384528</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2152,6 +2227,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384529</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386360</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389297</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,6 +2533,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389298</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389299</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405568</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2734,6 +2839,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384603</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,6 +2941,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389455</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2928,6 +3043,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405618</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3029,6 +3149,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610352</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3130,6 +3255,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610909</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3231,6 +3361,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610389</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3332,6 +3467,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610981</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3439,6 +3579,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602601</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3536,6 +3681,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405591</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3637,6 +3787,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610386</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3734,6 +3889,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386956</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3841,6 +4001,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602682</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3938,6 +4103,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711135</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4035,6 +4205,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386952</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4132,6 +4307,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386953</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4229,6 +4409,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610931</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4336,6 +4521,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599069</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4433,6 +4623,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389367</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4549,6 +4744,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601450</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4656,6 +4856,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602742</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4763,6 +4968,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602837</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4870,6 +5080,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119605491</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4971,6 +5186,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610016</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5072,6 +5292,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610035</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5173,6 +5398,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610049</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5274,6 +5504,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610170</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5375,6 +5610,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610345</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5476,6 +5716,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610370</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5577,6 +5822,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610414</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5678,6 +5928,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610423</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5779,6 +6034,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610496</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5880,6 +6140,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610555</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5981,6 +6246,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610595</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6082,6 +6352,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610873</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6179,6 +6454,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610933</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6276,6 +6556,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127297096</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6373,6 +6658,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127373664</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6470,6 +6760,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384583</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6567,6 +6862,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384584</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6664,6 +6964,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384592</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6761,6 +7066,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386377</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6858,6 +7168,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386384</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6955,6 +7270,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386385</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7052,6 +7372,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386386</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7149,6 +7474,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386387</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7246,6 +7576,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386944</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7343,6 +7678,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386946</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7440,6 +7780,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387142</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7537,6 +7882,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387353</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7634,6 +7984,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389432</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7731,6 +8086,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389445</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7828,6 +8188,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389446</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7925,6 +8290,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389447</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8032,6 +8402,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996516</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8133,6 +8508,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610685</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8240,6 +8620,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119596554</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8347,6 +8732,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119597037</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8448,6 +8838,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610217</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8549,6 +8944,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610249</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8650,6 +9050,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610392</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8751,6 +9156,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610474</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8852,6 +9262,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610491</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8953,6 +9368,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610633</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9054,6 +9474,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610668</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9155,6 +9580,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610831</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9256,6 +9686,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610869</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9357,6 +9792,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610921</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9458,6 +9898,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611238</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9559,6 +10004,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611239</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9660,6 +10110,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611240</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9757,6 +10212,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711138</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9855,6 +10315,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384605</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9953,6 +10418,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384606</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10051,6 +10521,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384607</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10149,6 +10624,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384608</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10246,6 +10726,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384610</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10343,6 +10828,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387358</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10440,6 +10930,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387359</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10537,6 +11032,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389457</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10634,6 +11134,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389458</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10731,6 +11236,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389459</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10828,6 +11338,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389460</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10929,6 +11444,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610034</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11030,6 +11550,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610177</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11131,6 +11656,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610545</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11228,6 +11758,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711128</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11325,6 +11860,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387129</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11432,6 +11972,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119596425</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11539,6 +12084,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119596942</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11646,6 +12196,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601364</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11753,6 +12308,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602051</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11860,6 +12420,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602150</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11967,6 +12532,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602704</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12074,6 +12644,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602950</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12181,6 +12756,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603156</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12288,6 +12868,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603303</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12395,6 +12980,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119604336</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12502,6 +13092,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119604600</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12609,6 +13204,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119604679</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12710,6 +13310,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610198</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12811,6 +13416,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610213</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12912,6 +13522,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610250</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13013,6 +13628,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610293</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13114,6 +13734,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610332</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13215,6 +13840,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610445</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13316,6 +13946,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610494</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13417,6 +14052,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610507</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13518,6 +14158,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610603</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13619,6 +14264,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610629</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13720,6 +14370,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610650</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13821,6 +14476,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610703</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13922,6 +14582,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610718</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14023,6 +14688,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610737</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14124,6 +14794,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610770</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14221,6 +14896,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610932</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14322,6 +15002,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610989</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14423,6 +15108,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610996</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14524,6 +15214,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611237</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14622,6 +15317,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611643</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14719,6 +15419,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611649</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14816,6 +15521,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611651</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14914,6 +15624,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611795</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15012,6 +15727,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611796</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15109,6 +15829,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711134</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15206,6 +15931,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127373662</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15303,6 +16033,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384573</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15400,6 +16135,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384577</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15497,6 +16237,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384578</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15594,6 +16339,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384579</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15691,6 +16441,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384580</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15788,6 +16543,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384581</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15885,6 +16645,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384582</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15982,6 +16747,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386372</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16079,6 +16849,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386373</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16176,6 +16951,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386374</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16273,6 +17053,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386705</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16370,6 +17155,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387141</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16468,6 +17258,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387330</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16565,6 +17360,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387345</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16662,6 +17462,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387351</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16759,6 +17564,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387352</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16856,6 +17666,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389403</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16953,6 +17768,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389404</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17050,6 +17870,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389407</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17147,6 +17972,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389408</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17244,6 +18074,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389409</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17341,6 +18176,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389410</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17438,6 +18278,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389411</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17535,6 +18380,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389412</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17632,6 +18482,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389413</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17729,6 +18584,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389414</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17826,6 +18686,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389415</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17923,6 +18788,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389416</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18020,6 +18890,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389418</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18117,6 +18992,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389419</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18214,6 +19094,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389420</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18311,6 +19196,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389421</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18408,6 +19298,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389422</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18505,6 +19400,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389423</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18602,6 +19502,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389424</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18699,6 +19604,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389425</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18796,6 +19706,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405608</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18893,6 +19808,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405609</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18990,6 +19910,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405610</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19087,6 +20012,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405611</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19194,6 +20124,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996520</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19301,6 +20236,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119596413</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19408,6 +20348,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119596616</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19509,6 +20454,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610273</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19610,6 +20560,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610322</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19711,6 +20666,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610432</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19812,6 +20772,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610514</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19913,6 +20878,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610752</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20014,6 +20984,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610790</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20115,6 +21090,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610885</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20212,6 +21192,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711129</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20309,6 +21294,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711130</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20406,6 +21396,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711131</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20503,6 +21498,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384536</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20600,6 +21600,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384537</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20697,6 +21702,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387131</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20794,6 +21804,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387328</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20891,6 +21906,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387329</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20988,6 +22008,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389304</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21085,6 +22110,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389305</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21182,6 +22212,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389307</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21279,6 +22314,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389308</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21376,6 +22416,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389309</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21473,6 +22518,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389310</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21570,6 +22620,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389311</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21667,6 +22722,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389312</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21764,6 +22824,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389313</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21861,6 +22926,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389314</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21958,6 +23028,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389316</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22055,6 +23130,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389317</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22152,6 +23232,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389318</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22249,6 +23334,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389319</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22346,6 +23436,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389320</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22443,6 +23538,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389321</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22540,6 +23640,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389322</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22637,6 +23742,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389323</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22734,6 +23844,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389324</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -22831,6 +23946,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389325</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -22928,6 +24048,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389326</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23025,6 +24150,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389327</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23122,6 +24252,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389328</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23219,6 +24354,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389329</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23316,6 +24456,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389330</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23413,6 +24558,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389331</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23510,6 +24660,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389332</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23607,6 +24762,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389333</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23704,6 +24864,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389334</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -23801,6 +24966,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389335</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -23898,6 +25068,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389336</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -23995,6 +25170,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389337</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24092,6 +25272,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389338</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24189,6 +25374,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389339</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24286,6 +25476,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389341</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24383,6 +25578,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405570</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24480,6 +25680,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405571</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24577,6 +25782,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405572</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24684,6 +25894,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599257</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -24796,6 +26011,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599717</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -24903,6 +26123,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601593</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -25010,6 +26235,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602566</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25107,6 +26337,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389402</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25208,6 +26443,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610054</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25309,6 +26549,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610164</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25410,6 +26655,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610535</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25511,6 +26761,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610808</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25608,6 +26863,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389365</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25705,6 +26965,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389366</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -25802,6 +27067,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405587</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -25903,6 +27173,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610665</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -26004,6 +27279,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610901</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -26101,6 +27381,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711137</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -26208,6 +27493,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602844</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -26313,6 +27603,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610787</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26423,6 +27718,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611786</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26525,6 +27825,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127373638</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26630,6 +27935,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386363</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -26735,6 +28045,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387128</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -26840,6 +28155,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405583</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -26945,6 +28265,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387380</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -27052,6 +28377,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602982</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -27149,6 +28479,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127289948</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -27258,6 +28593,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384547</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -27367,6 +28707,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384551</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -27472,6 +28817,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387134</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -27581,6 +28931,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389360</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -27690,6 +29045,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389361</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -27792,6 +29152,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386909</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -27889,6 +29254,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384600</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -27986,6 +29356,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386388</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -28083,6 +29458,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386390</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -28181,6 +29561,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387356</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -28279,6 +29664,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387383</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -28377,6 +29767,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405615</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -28479,6 +29874,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611788</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -28576,6 +29976,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386932</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -28678,6 +30083,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610005</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -28775,6 +30185,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386919</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -28872,6 +30287,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405588</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -28970,6 +30390,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610098</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -29077,6 +30502,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119596798</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -29184,6 +30614,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602089</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -29291,6 +30726,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602128</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -29398,6 +30838,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119604694</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -29499,6 +30944,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610193</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -29600,6 +31050,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610222</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -29701,6 +31156,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610334</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -29802,6 +31262,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610601</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -29903,6 +31368,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610670</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -30004,6 +31474,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610700</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -30105,6 +31580,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610721</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -30206,6 +31686,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610730</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -30307,6 +31792,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610903</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -30405,6 +31895,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611645</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -30502,6 +31997,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611646</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -30599,6 +32099,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611647</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -30696,6 +32201,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611648</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -30799,6 +32309,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611790</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -30897,6 +32412,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611791</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -31000,6 +32520,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611792</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -31098,6 +32623,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711132</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -31195,6 +32725,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711133</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -31292,6 +32827,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127289924</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -31389,6 +32929,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127290144</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -31486,6 +33031,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127296819</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -31583,6 +33133,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127296988</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -31680,6 +33235,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384557</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -31777,6 +33337,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384558</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -31874,6 +33439,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384559</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -31971,6 +33541,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384561</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -32068,6 +33643,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384565</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -32165,6 +33745,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384566</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -32262,6 +33847,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384567</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -32359,6 +33949,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384568</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -32456,6 +34051,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384570</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -32553,6 +34153,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384571</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -32650,6 +34255,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386366</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -32747,6 +34357,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386367</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -32844,6 +34459,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386368</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -32941,6 +34561,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127386371</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -33038,6 +34663,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387137</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -33135,6 +34765,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387333</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -33232,6 +34867,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387334</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -33329,6 +34969,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387335</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -33426,6 +35071,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387336</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -33523,6 +35173,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387341</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -33620,6 +35275,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387342</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -33717,6 +35377,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387343</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -33814,6 +35479,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387344</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -33911,6 +35581,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127387382</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -34008,6 +35683,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389368</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -34105,6 +35785,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389369</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -34202,6 +35887,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389370</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -34299,6 +35989,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389371</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -34396,6 +36091,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389375</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -34493,6 +36193,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389376</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -34590,6 +36295,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389377</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -34687,6 +36397,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389378</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -34784,6 +36499,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389379</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -34881,6 +36601,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389380</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -34978,6 +36703,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389381</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -35075,6 +36805,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389382</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -35172,6 +36907,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389383</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -35269,6 +37009,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389384</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -35366,6 +37111,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389385</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -35463,6 +37213,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389386</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -35560,6 +37315,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389387</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -35657,6 +37417,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389388</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -35754,6 +37519,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389389</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -35851,6 +37621,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389390</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -35948,6 +37723,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389391</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -36045,6 +37825,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405595</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -36142,6 +37927,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405596</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -36239,6 +38029,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405597</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -36336,6 +38131,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405601</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -36433,6 +38233,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405602</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -36540,6 +38345,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996518</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -36647,6 +38457,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119604415</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -36748,6 +38563,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610400</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -36849,6 +38669,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610764</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -36950,6 +38775,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610850</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -37051,6 +38881,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610964</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -37148,6 +38983,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127289839</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -37245,6 +39085,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127373629</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -37343,6 +39188,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384533</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -37440,6 +39290,11 @@
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384538</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -37537,6 +39392,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384540</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -37634,6 +39494,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384541</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -37731,6 +39596,11 @@
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127384543</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -37828,6 +39698,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389342</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -37925,6 +39800,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389343</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -38022,6 +39902,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389344</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -38119,6 +40004,11 @@
         </is>
       </c>
       <c r="AY378" t="inlineStr"/>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389345</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -38216,6 +40106,11 @@
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389346</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -38313,6 +40208,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389347</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -38410,6 +40310,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389348</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -38507,6 +40412,11 @@
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389349</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -38604,6 +40514,11 @@
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389350</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -38701,6 +40616,11 @@
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389351</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -38798,6 +40718,11 @@
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389352</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -38895,6 +40820,11 @@
         </is>
       </c>
       <c r="AY386" t="inlineStr"/>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389353</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -38992,6 +40922,11 @@
         </is>
       </c>
       <c r="AY387" t="inlineStr"/>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405578</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -39090,8 +41025,402 @@
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127405582</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>